--- a/backend/機能要件_アーキテクチャ選定マッピング_v2.xlsx
+++ b/backend/機能要件_アーキテクチャ選定マッピング_v2.xlsx
@@ -617,12 +617,12 @@
           <t>C-AWS_備考</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="18" t="inlineStr">
         <is>
           <t>実装状況(2026-08-28時点)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="18" t="inlineStr">
         <is>
           <t>判定根拠</t>
         </is>
@@ -682,12 +682,12 @@
           <t>Cognitoユーザープール+グループで6区分に対応可能(設計・実装は必要)</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
+      <c r="L2" s="18" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="M2" s="18" t="inlineStr">
         <is>
           <t>create_security_roles.py + verify_security_roles.pyで6区分ロール・95権限を構築・検証済み</t>
         </is>
@@ -747,12 +747,12 @@
           <t>Cognito標準管理機能で対応</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
+      <c r="L3" s="18" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="M3" s="18" t="inlineStr">
         <is>
           <t>Dataverse/Entra ID標準機能(追加実装不要)</t>
         </is>
@@ -812,12 +812,12 @@
           <t>Cognitoグループ管理用の管理画面を別途実装する必要あり</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
+      <c r="L4" s="18" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="M4" s="18" t="inlineStr">
         <is>
           <t>セキュリティロールはノーコードで編集可能(標準機能)</t>
         </is>
@@ -877,12 +877,12 @@
           <t>フロントエンド(React等)でロール別表示制御を実装</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L5" s="18" t="inlineStr">
         <is>
           <t>✗</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M5" s="18" t="inlineStr">
         <is>
           <t>ロール別サイトマップ/メニュー出し分けの設計・実装は未着手</t>
         </is>
@@ -942,12 +942,12 @@
           <t>フロントエンド設計で対応</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L6" s="18" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M6" s="18" t="inlineStr">
         <is>
           <t>モデル駆動アプリ自体は稼働中だが、全機能を網羅したメニュー構成は未検証</t>
         </is>
@@ -1007,12 +1007,12 @@
           <t>AppSync/GraphQLスキーマ定義とDB設計が必要(要実装)</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
+      <c r="L7" s="18" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="M7" s="18" t="inlineStr">
         <is>
           <t>tree/diagnosis/inspection/workhistoryテーブルで実装済み</t>
         </is>
@@ -1072,12 +1072,12 @@
           <t>DynamoDB/Aurora上でのテーブル設計・実装が必要</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
+      <c r="L8" s="18" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="M8" s="18" t="inlineStr">
         <is>
           <t>workhistoryテーブル+TreeIdルックアップ(1:N)で実装済み</t>
         </is>
@@ -1137,12 +1137,12 @@
           <t>AppSyncリゾルバでの権限制御ロジック実装が必要</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
+      <c r="L9" s="18" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="M9" s="18" t="inlineStr">
         <is>
           <t>セキュリティロールのCRU権限で制御済み</t>
         </is>
@@ -1202,14 +1202,14 @@
           <t>S3+Amplify Storageで標準的に対応可能</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>【要注意】diagnosisには添付ファイル列があるが、workhistory(作業履歴)には写真列が無い。作業前後写真を厳密に満たすには追加実装が必要</t>
+      <c r="L10" s="18" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="M10" s="18" t="inlineStr">
+        <is>
+          <t>workhistoryはHasNotes=True(Dataverse標準の添付機能)で実装済み。ユーザー確認により訂正(2026-08-28)。専用の写真列は不要と判断</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
           <t>DynamoDB StreamsやDB監査ログの実装が必要</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="L11" s="18" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="M11" s="18" t="inlineStr">
         <is>
           <t>Dataverse監査(Audit)機能は標準搭載。ただし本環境での有効化・動作確認は未実施</t>
         </is>
@@ -1332,12 +1332,12 @@
           <t>Lambda関数によるインポート/エクスポート処理を個別実装</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L12" s="18" t="inlineStr">
         <is>
           <t>✗</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M12" s="18" t="inlineStr">
         <is>
           <t>CSV/Excel/PDF入出力(Power Automate等)の実装は未着手</t>
         </is>
@@ -1397,12 +1397,12 @@
           <t>AppSync GraphQL APIが外部連携の標準的な窓口になる</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
+      <c r="L13" s="18" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="M13" s="18" t="inlineStr">
         <is>
           <t>Dataverse Web APIで標準的に満たす(create_*.py自体がその実証)</t>
         </is>
@@ -1462,12 +1462,12 @@
           <t>カレンダーUIをフロントエンドで個別実装する必要あり</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L14" s="18" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M14" s="18" t="inlineStr">
         <is>
           <t>complaint/workhistoryテーブルはあるが、カレンダービュー・期間検索ビューは未構築</t>
         </is>
@@ -1527,12 +1527,12 @@
           <t>単純なテキストフィールドで標準対応</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
+      <c r="L15" s="18" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="M15" s="18" t="inlineStr">
         <is>
           <t>各テーブルにNotes等の自由記述列あり</t>
         </is>
@@ -1592,12 +1592,12 @@
           <t>S3経由での保存で標準対応</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
+      <c r="L16" s="18" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="M16" s="18" t="inlineStr">
         <is>
           <t>diagnosis.DiagnosisReportFile列で実装済み</t>
         </is>
@@ -1657,12 +1657,12 @@
           <t>Lambdaによる業務ロジックの個別実装が必要</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
+      <c r="L17" s="18" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="M17" s="18" t="inlineStr">
         <is>
           <t>replant.ReplantFromTreeId + Power Automateで実装・動作確認済み(README記載)</t>
         </is>
@@ -1722,12 +1722,12 @@
           <t>履歴用テーブルの個別設計が必要</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
+      <c r="L18" s="18" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="M18" s="18" t="inlineStr">
         <is>
           <t>replantテーブルでOldTreeId保持、旧樹木ステータス自動更新も実装済み</t>
         </is>
@@ -1787,12 +1787,12 @@
           <t>ソフトデリート機構をアプリ側で個別実装する必要あり</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="L19" s="18" t="inlineStr">
         <is>
           <t>？</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="M19" s="18" t="inlineStr">
         <is>
           <t>Dataverse標準のソフトデリート機能はあるが、有効化・動作確認は未実施</t>
         </is>
@@ -1852,12 +1852,12 @@
           <t>OpenSearch連携等の検索基盤を個別実装する必要あり</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
+      <c r="L20" s="18" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="M20" s="18" t="inlineStr">
         <is>
           <t>Dataverseの高度な検索・ビューは標準機能(個別実装不要)</t>
         </is>
@@ -1917,12 +1917,12 @@
           <t>集計用Lambda/クエリを個別実装する必要あり</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="L21" s="18" t="inlineStr">
         <is>
           <t>✗</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M21" s="18" t="inlineStr">
         <is>
           <t>集計ビュー/Power BI連携は未着手</t>
         </is>
@@ -1982,12 +1982,12 @@
           <t>Cognitoの外部ユーザープールで標準的に対応可能</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
+      <c r="L22" s="18" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="M22" s="18" t="inlineStr">
         <is>
           <t>「街路樹管理委託事業者」ロールで担当エリア単位のCRU権限を実装・検証済み</t>
         </is>
@@ -2047,12 +2047,12 @@
           <t>Amplifyでモバイル/PWA対応は可能だがアプリ実装が必要</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="L23" s="18" t="inlineStr">
         <is>
           <t>？</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="M23" s="18" t="inlineStr">
         <is>
           <t>Power Appsモバイルアプリでの実機動作確認は未実施</t>
         </is>
@@ -2112,12 +2112,12 @@
           <t>フロントエンド/リゾルバでのバリデーション実装が必要</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="L24" s="18" t="inlineStr">
         <is>
           <t>？</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="M24" s="18" t="inlineStr">
         <is>
           <t>ビジネスルール・必須項目設定の実装有無は未確認</t>
         </is>
@@ -2177,12 +2177,12 @@
           <t>予定管理機能をアプリ側で個別実装する必要あり</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="L25" s="18" t="inlineStr">
         <is>
           <t>✗</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="M25" s="18" t="inlineStr">
         <is>
           <t>予定管理ロジック(Power Automate)は未着手</t>
         </is>
@@ -2242,12 +2242,12 @@
           <t>Lambda+PDFライブラリで個別実装する必要あり</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="L26" s="18" t="inlineStr">
         <is>
           <t>✗</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M26" s="18" t="inlineStr">
         <is>
           <t>様式出力の実装は未着手</t>
         </is>
@@ -2307,12 +2307,12 @@
           <t>Amazon Location Serviceの地図表示は標準機能</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
+      <c r="L27" s="18" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="M27" s="18" t="inlineStr">
         <is>
           <t>TreeMapControl(PCF)でBubbleLayer表示・動作確認済み(2026-08-28)</t>
         </is>
@@ -2372,12 +2372,12 @@
           <t>Location Service SDKでのカスタム実装が必要</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="L28" s="18" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="M28" s="18" t="inlineStr">
         <is>
           <t>【仕様と差異】現状は常時ラベル表示(SymbolLayer)。「カーソルオン時のみ表示」ではない</t>
         </is>
@@ -2437,12 +2437,12 @@
           <t>フロントエンドでの画面遷移ロジックを個別実装</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="L29" s="18" t="inlineStr">
         <is>
           <t>✗</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M29" s="18" t="inlineStr">
         <is>
           <t>TreeMap.tsxにクリックイベントハンドラなし。ポイントクリックでの画面遷移は未実装</t>
         </is>
@@ -2502,12 +2502,12 @@
           <t>Location Service SDKを用いたカスタム実装が必要</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="L30" s="18" t="inlineStr">
         <is>
           <t>✗</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="M30" s="18" t="inlineStr">
         <is>
           <t>地図上からの新規登録機能なし(現状は読み取り専用の表示のみ)</t>
         </is>
@@ -2567,12 +2567,12 @@
           <t>ドラッグ&amp;ドロップの地図操作をSDKレベルで個別実装する必要あり</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="L31" s="18" t="inlineStr">
         <is>
           <t>✗</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="M31" s="18" t="inlineStr">
         <is>
           <t>ドラッグによる位置修正コードなし</t>
         </is>
@@ -2632,12 +2632,12 @@
           <t>Location Service SDKのイベントで取得可能(実装要)</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="L32" s="18" t="inlineStr">
         <is>
           <t>✗</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="M32" s="18" t="inlineStr">
         <is>
           <t>30と連動。ドラッグ先座標取得コードなし</t>
         </is>
@@ -2697,12 +2697,12 @@
           <t>権限制御とレイヤー切替をアプリ側で個別実装</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="L33" s="18" t="inlineStr">
         <is>
           <t>✗</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="M33" s="18" t="inlineStr">
         <is>
           <t>新設/撤去に応じた表示切替コードなし</t>
         </is>
@@ -2762,12 +2762,12 @@
           <t>ブラウザ/モバイルの位置情報APIで標準的に取得可能</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="L34" s="18" t="inlineStr">
         <is>
           <t>✗</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="M34" s="18" t="inlineStr">
         <is>
           <t>位置情報自動取得コードなし</t>
         </is>
@@ -2827,12 +2827,12 @@
           <t>ソフトデリート機構を個別実装する必要あり</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="L35" s="18" t="inlineStr">
         <is>
           <t>？</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="M35" s="18" t="inlineStr">
         <is>
           <t>18と同様、ソフトデリートの有効化・動作確認は未実施</t>
         </is>
@@ -2892,12 +2892,12 @@
           <t>検索機能を個別実装する必要あり</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
+      <c r="L36" s="18" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="M36" s="18" t="inlineStr">
         <is>
           <t>Dataverseの高度な検索は標準機能(個別実装不要)</t>
         </is>

--- a/backend/機能要件_アーキテクチャ選定マッピング_v2.xlsx
+++ b/backend/機能要件_アーキテクチャ選定マッピング_v2.xlsx
@@ -2439,12 +2439,12 @@
       </c>
       <c r="L29" s="18" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M29" s="18" t="inlineStr">
         <is>
-          <t>TreeMap.tsxにクリックイベントハンドラなし。ポイントクリックでの画面遷移は未実装</t>
+          <t>ポイントクリックでcontext.navigation.openForm()により詳細画面へ遷移する実装・動作確認済み(2026-08-28)</t>
         </is>
       </c>
     </row>
@@ -2504,12 +2504,12 @@
       </c>
       <c r="L30" s="18" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M30" s="18" t="inlineStr">
         <is>
-          <t>地図上からの新規登録機能なし(現状は読み取り専用の表示のみ)</t>
+          <t>作成権限(Create/Global)がある場合、空き地クリックでwebAPI.createRecord()により新規作成し詳細フォームを開く実装・動作確認済み(2026-08-28)</t>
         </is>
       </c>
     </row>
@@ -2569,12 +2569,12 @@
       </c>
       <c r="L31" s="18" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M31" s="18" t="inlineStr">
         <is>
-          <t>ドラッグによる位置修正コードなし</t>
+          <t>更新権限(Write/Global)がある場合、ポイントのドラッグで位置修正可能。実装・動作確認済み(2026-08-28)</t>
         </is>
       </c>
     </row>
@@ -2634,12 +2634,12 @@
       </c>
       <c r="L32" s="18" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M32" s="18" t="inlineStr">
         <is>
-          <t>30と連動。ドラッグ先座標取得コードなし</t>
+          <t>#30と同時実装。ドラッグ終了時の座標をwebAPI.updateRecord()でDataverseへ反映済み(2026-08-28)</t>
         </is>
       </c>
     </row>
@@ -2699,12 +2699,12 @@
       </c>
       <c r="L33" s="18" t="inlineStr">
         <is>
-          <t>✗</t>
+          <t>◎</t>
         </is>
       </c>
       <c r="M33" s="18" t="inlineStr">
         <is>
-          <t>新設/撤去に応じた表示切替コードなし</t>
+          <t>既存の再描画の仕組み(データセット変更時の自動再同期)で対応。あわせて全件が表示されない不具合(ページング設定が初回ロードに間に合わない)も修正済み(2026-08-28)</t>
         </is>
       </c>
     </row>
